--- a/ArduinoIDE/_Project/SelfDrivingCar/CarModule/array.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/CarModule/array.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Maker\ArduinoSample\ArduinoIDE\AStar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\CarModule\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06C1A0C-9C5D-4D44-A6DC-5C1AE57137A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4476" yWindow="2412" windowWidth="7656" windowHeight="6396"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>(0,0)</t>
   </si>
@@ -59,12 +60,24 @@
     <t>→</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>唯讀：只能改倉庫、充電、客戶底色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯讀：只能數字0,1，底色會自動改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯讀：陣列自動產生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -87,6 +100,14 @@
       <name val="王漢宗波卡體一空陰"/>
       <family val="1"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -162,7 +183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -190,11 +211,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -514,17 +551,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" customWidth="1"/>
-    <col min="2" max="6" width="5.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" customWidth="1"/>
-    <col min="8" max="16" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="6" width="5.625" customWidth="1"/>
+    <col min="7" max="7" width="5.875" customWidth="1"/>
+    <col min="8" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="B1">
         <v>0</v>
       </c>
@@ -565,7 +602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
@@ -625,7 +662,7 @@
         <v>(0,7)</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -685,7 +722,7 @@
         <v>(1,7)</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
@@ -745,7 +782,7 @@
         <v>(2,7)</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>3</v>
       </c>
@@ -805,7 +842,7 @@
         <v>(3,7)</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
@@ -865,7 +902,7 @@
         <v>(4,7)</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17">
       <c r="H7">
         <v>5</v>
       </c>
@@ -902,7 +939,7 @@
         <v>(5,7)</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17">
       <c r="H8">
         <v>6</v>
       </c>
@@ -939,7 +976,7 @@
         <v>(6,7)</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17">
       <c r="H9">
         <v>7</v>
       </c>
@@ -976,295 +1013,321 @@
         <v>(7,7)</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
+    <row r="10" spans="1:17">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="B11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>2</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>3</v>
       </c>
-      <c r="N11">
+      <c r="N12">
         <v>4</v>
       </c>
-      <c r="O11">
+      <c r="O12">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" s="5" t="str">
-        <f>"("&amp;$A12&amp;","&amp;I$1&amp;")"</f>
+    <row r="13" spans="1:17">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f t="shared" ref="B13:G16" si="4">"("&amp;$A13&amp;","&amp;I$1&amp;")"</f>
         <v>(0,0)</v>
       </c>
-      <c r="C12" s="4" t="str">
-        <f>"("&amp;$A12&amp;","&amp;J$1&amp;")"</f>
+      <c r="C13" s="9" t="str">
+        <f t="shared" si="4"/>
         <v>(0,1)</v>
       </c>
-      <c r="D12" s="3" t="str">
-        <f>"("&amp;$A12&amp;","&amp;K$1&amp;")"</f>
+      <c r="D13" s="9" t="str">
+        <f t="shared" ref="D13:F16" si="5">"("&amp;$A13&amp;","&amp;K$1&amp;")"</f>
         <v>(0,2)</v>
       </c>
-      <c r="E12" s="4" t="str">
-        <f>"("&amp;$A12&amp;","&amp;L$1&amp;")"</f>
+      <c r="E13" s="9" t="str">
+        <f t="shared" ref="E13:F16" si="6">"("&amp;$A13&amp;","&amp;L$1&amp;")"</f>
         <v>(0,3)</v>
       </c>
-      <c r="F12" s="4" t="str">
-        <f>"("&amp;$A12&amp;","&amp;M$1&amp;")"</f>
+      <c r="F13" s="9" t="str">
+        <f t="shared" ref="F13:F16" si="7">"("&amp;$A13&amp;","&amp;M$1&amp;")"</f>
         <v>(0,4)</v>
       </c>
-      <c r="G12" s="4" t="str">
-        <f>"("&amp;$A12&amp;","&amp;N$1&amp;")"</f>
+      <c r="G13" s="7" t="str">
+        <f t="shared" si="4"/>
         <v>(0,5)</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="str">
-        <f>"{"&amp;J12&amp;","&amp;K12&amp;","&amp;L12&amp;","&amp;M12&amp;","&amp;N12&amp;","&amp;O12&amp;"},"</f>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9">
+        <v>1</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="str">
+        <f>"{"&amp;J13&amp;","&amp;K13&amp;","&amp;L13&amp;","&amp;M13&amp;","&amp;N13&amp;","&amp;O13&amp;"},"</f>
         <v>{1,1,0,1,1,1},</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="str">
-        <f>"("&amp;$A13&amp;","&amp;I$1&amp;")"</f>
+    <row r="14" spans="1:17">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <f t="shared" si="4"/>
         <v>(1,0)</v>
       </c>
-      <c r="C13" s="3" t="str">
-        <f>"("&amp;$A13&amp;","&amp;J$1&amp;")"</f>
+      <c r="C14" s="9" t="str">
+        <f t="shared" ref="C14:F16" si="8">"("&amp;$A14&amp;","&amp;J$1&amp;")"</f>
         <v>(1,1)</v>
       </c>
-      <c r="D13" s="3" t="str">
-        <f>"("&amp;$A13&amp;","&amp;K$1&amp;")"</f>
+      <c r="D14" s="9" t="str">
+        <f t="shared" si="5"/>
         <v>(1,2)</v>
       </c>
-      <c r="E13" s="4" t="str">
-        <f>"("&amp;$A13&amp;","&amp;L$1&amp;")"</f>
+      <c r="E14" s="9" t="str">
+        <f t="shared" si="6"/>
         <v>(1,3)</v>
       </c>
-      <c r="F13" s="3" t="str">
-        <f>"("&amp;$A13&amp;","&amp;M$1&amp;")"</f>
+      <c r="F14" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>(1,4)</v>
       </c>
-      <c r="G13" s="4" t="str">
-        <f>"("&amp;$A13&amp;","&amp;N$1&amp;")"</f>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="4"/>
         <v>(1,5)</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="str">
-        <f t="shared" ref="Q13:Q15" si="4">"{"&amp;J13&amp;","&amp;K13&amp;","&amp;L13&amp;","&amp;M13&amp;","&amp;N13&amp;","&amp;O13&amp;"},"</f>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" ref="Q14:Q15" si="9">"{"&amp;J14&amp;","&amp;K14&amp;","&amp;L14&amp;","&amp;M14&amp;","&amp;N14&amp;","&amp;O14&amp;"},"</f>
         <v>{1,0,0,1,0,1},</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="15" spans="1:17" ht="19.5">
+      <c r="A15">
         <v>2</v>
       </c>
-      <c r="B14" s="7" t="str">
-        <f>"("&amp;$A14&amp;","&amp;I$1&amp;")"</f>
+      <c r="B15" s="9" t="str">
+        <f t="shared" si="4"/>
         <v>(2,0)</v>
       </c>
-      <c r="C14" s="3" t="str">
-        <f>"("&amp;$A14&amp;","&amp;J$1&amp;")"</f>
+      <c r="C15" s="9" t="str">
+        <f t="shared" si="8"/>
         <v>(2,1)</v>
       </c>
-      <c r="D14" s="4" t="str">
-        <f>"("&amp;$A14&amp;","&amp;K$1&amp;")"</f>
+      <c r="D15" s="9" t="str">
+        <f t="shared" si="5"/>
         <v>(2,2)</v>
       </c>
-      <c r="E14" s="4" t="str">
-        <f>"("&amp;$A14&amp;","&amp;L$1&amp;")"</f>
+      <c r="E15" s="9" t="str">
+        <f t="shared" si="6"/>
         <v>(2,3)</v>
       </c>
-      <c r="F14" s="3" t="str">
-        <f>"("&amp;$A14&amp;","&amp;M$1&amp;")"</f>
+      <c r="F15" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>(2,4)</v>
       </c>
-      <c r="G14" s="4" t="str">
-        <f>"("&amp;$A14&amp;","&amp;N$1&amp;")"</f>
+      <c r="G15" s="4" t="str">
+        <f t="shared" si="4"/>
         <v>(2,5)</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1</v>
-      </c>
-      <c r="P14" s="8" t="s">
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>1</v>
+      </c>
+      <c r="M15" s="9">
+        <v>1</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="Q15" t="str">
+        <f t="shared" si="9"/>
+        <v>{1,0,1,1,0,1},</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>{1,0,1,1,0,1},</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15">
+        <v>(3,0)</v>
+      </c>
+      <c r="C16" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>(3,1)</v>
+      </c>
+      <c r="D16" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>(3,2)</v>
+      </c>
+      <c r="E16" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>(3,3)</v>
+      </c>
+      <c r="F16" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>(3,4)</v>
+      </c>
+      <c r="G16" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>(3,5)</v>
+      </c>
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f>"("&amp;$A15&amp;","&amp;I$1&amp;")"</f>
-        <v>(3,0)</v>
-      </c>
-      <c r="C15" s="4" t="str">
-        <f>"("&amp;$A15&amp;","&amp;J$1&amp;")"</f>
-        <v>(3,1)</v>
-      </c>
-      <c r="D15" s="4" t="str">
-        <f>"("&amp;$A15&amp;","&amp;K$1&amp;")"</f>
-        <v>(3,2)</v>
-      </c>
-      <c r="E15" s="3" t="str">
-        <f>"("&amp;$A15&amp;","&amp;L$1&amp;")"</f>
-        <v>(3,3)</v>
-      </c>
-      <c r="F15" s="3" t="str">
-        <f>"("&amp;$A15&amp;","&amp;M$1&amp;")"</f>
-        <v>(3,4)</v>
-      </c>
-      <c r="G15" s="6" t="str">
-        <f>"("&amp;$A15&amp;","&amp;N$1&amp;")"</f>
-        <v>(3,5)</v>
-      </c>
-      <c r="I15">
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9">
+        <v>1</v>
+      </c>
+      <c r="L16" s="9">
+        <v>1</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="str">
+        <f>"{"&amp;J16&amp;","&amp;K16&amp;","&amp;L16&amp;","&amp;M16&amp;","&amp;N16&amp;","&amp;O16&amp;"}"</f>
+        <v>{1,1,1,0,0,1}</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="str">
-        <f>"{"&amp;J15&amp;","&amp;K15&amp;","&amp;L15&amp;","&amp;M15&amp;","&amp;N15&amp;","&amp;O15&amp;"}"</f>
-        <v>{1,1,1,0,0,1}</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
+    <row r="20" spans="2:3">
+      <c r="B20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J12:O15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="J13:O16">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:F16">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>K13=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ArduinoIDE/_Project/SelfDrivingCar/CarModule/array.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/CarModule/array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\CarModule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06C1A0C-9C5D-4D44-A6DC-5C1AE57137A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2F26AF-F8D4-4C36-B2FC-6747D3AD4ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,19 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>(0,0)</t>
   </si>
   <si>
     <t>(2,0)</t>
-  </si>
-  <si>
-    <t>(3,5)</t>
-  </si>
-  <si>
-    <t>倉庫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>充電</t>
@@ -72,11 +65,38 @@
     <t>唯讀：陣列自動產生</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>物流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3,5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3,0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地圖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電線長度：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="General&quot;m&quot;"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="12"/>
@@ -110,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,6 +173,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -183,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -196,9 +222,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -211,20 +234,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -552,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.875" customWidth="1"/>
@@ -1014,24 +1075,24 @@
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="9" t="s">
         <v>7</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1072,53 +1133,53 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="39.950000000000003" customHeight="1">
       <c r="A13">
         <v>0</v>
       </c>
-      <c r="B13" s="5" t="str">
+      <c r="B13" s="10" t="str">
         <f t="shared" ref="B13:G16" si="4">"("&amp;$A13&amp;","&amp;I$1&amp;")"</f>
         <v>(0,0)</v>
       </c>
-      <c r="C13" s="9" t="str">
+      <c r="C13" s="11" t="str">
         <f t="shared" si="4"/>
         <v>(0,1)</v>
       </c>
-      <c r="D13" s="9" t="str">
-        <f t="shared" ref="D13:F16" si="5">"("&amp;$A13&amp;","&amp;K$1&amp;")"</f>
+      <c r="D13" s="11" t="str">
+        <f t="shared" ref="D13:D16" si="5">"("&amp;$A13&amp;","&amp;K$1&amp;")"</f>
         <v>(0,2)</v>
       </c>
-      <c r="E13" s="9" t="str">
-        <f t="shared" ref="E13:F16" si="6">"("&amp;$A13&amp;","&amp;L$1&amp;")"</f>
+      <c r="E13" s="11" t="str">
+        <f t="shared" ref="E13:E16" si="6">"("&amp;$A13&amp;","&amp;L$1&amp;")"</f>
         <v>(0,3)</v>
       </c>
-      <c r="F13" s="9" t="str">
+      <c r="F13" s="11" t="str">
         <f t="shared" ref="F13:F16" si="7">"("&amp;$A13&amp;","&amp;M$1&amp;")"</f>
         <v>(0,4)</v>
       </c>
-      <c r="G13" s="7" t="str">
+      <c r="G13" s="12" t="str">
         <f t="shared" si="4"/>
         <v>(0,5)</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="9">
-        <v>1</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="J13" s="15">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11">
         <v>0</v>
       </c>
-      <c r="M13" s="9">
-        <v>1</v>
-      </c>
-      <c r="N13" s="9">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
+      <c r="M13" s="11">
+        <v>1</v>
+      </c>
+      <c r="N13" s="11">
+        <v>1</v>
+      </c>
+      <c r="O13" s="15">
         <v>1</v>
       </c>
       <c r="Q13" t="str">
@@ -1126,53 +1187,53 @@
         <v>{1,1,0,1,1,1},</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="39.950000000000003" customHeight="1">
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B14" s="13" t="str">
         <f t="shared" si="4"/>
         <v>(1,0)</v>
       </c>
-      <c r="C14" s="9" t="str">
-        <f t="shared" ref="C14:F16" si="8">"("&amp;$A14&amp;","&amp;J$1&amp;")"</f>
+      <c r="C14" s="11" t="str">
+        <f t="shared" ref="C14:C16" si="8">"("&amp;$A14&amp;","&amp;J$1&amp;")"</f>
         <v>(1,1)</v>
       </c>
-      <c r="D14" s="9" t="str">
+      <c r="D14" s="11" t="str">
         <f t="shared" si="5"/>
         <v>(1,2)</v>
       </c>
-      <c r="E14" s="9" t="str">
+      <c r="E14" s="11" t="str">
         <f t="shared" si="6"/>
         <v>(1,3)</v>
       </c>
-      <c r="F14" s="9" t="str">
+      <c r="F14" s="11" t="str">
         <f t="shared" si="7"/>
         <v>(1,4)</v>
       </c>
-      <c r="G14" s="4" t="str">
+      <c r="G14" s="13" t="str">
         <f t="shared" si="4"/>
         <v>(1,5)</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9">
+      <c r="J14" s="15">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11">
         <v>0</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="11">
         <v>0</v>
       </c>
-      <c r="M14" s="9">
-        <v>1</v>
-      </c>
-      <c r="N14" s="9">
+      <c r="M14" s="11">
+        <v>1</v>
+      </c>
+      <c r="N14" s="11">
         <v>0</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="15">
         <v>1</v>
       </c>
       <c r="Q14" t="str">
@@ -1180,113 +1241,113 @@
         <v>{1,0,0,1,0,1},</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="19.5">
+    <row r="15" spans="1:17" ht="39.950000000000003" customHeight="1">
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="9" t="str">
+      <c r="B15" s="11" t="str">
         <f t="shared" si="4"/>
         <v>(2,0)</v>
       </c>
-      <c r="C15" s="9" t="str">
+      <c r="C15" s="11" t="str">
         <f t="shared" si="8"/>
         <v>(2,1)</v>
       </c>
-      <c r="D15" s="9" t="str">
+      <c r="D15" s="11" t="str">
         <f t="shared" si="5"/>
         <v>(2,2)</v>
       </c>
-      <c r="E15" s="9" t="str">
+      <c r="E15" s="11" t="str">
         <f t="shared" si="6"/>
         <v>(2,3)</v>
       </c>
-      <c r="F15" s="9" t="str">
+      <c r="F15" s="11" t="str">
         <f t="shared" si="7"/>
         <v>(2,4)</v>
       </c>
-      <c r="G15" s="4" t="str">
+      <c r="G15" s="13" t="str">
         <f t="shared" si="4"/>
         <v>(2,5)</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>6</v>
+      <c r="H15" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="9">
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="11">
         <v>0</v>
       </c>
-      <c r="L15" s="9">
-        <v>1</v>
-      </c>
-      <c r="M15" s="9">
-        <v>1</v>
-      </c>
-      <c r="N15" s="9">
+      <c r="L15" s="11">
+        <v>1</v>
+      </c>
+      <c r="M15" s="11">
+        <v>1</v>
+      </c>
+      <c r="N15" s="11">
         <v>0</v>
       </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>6</v>
+      <c r="O15" s="15">
+        <v>1</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="9"/>
         <v>{1,0,1,1,0,1},</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
-      <c r="A16">
+    <row r="16" spans="1:17" ht="39.950000000000003" customHeight="1">
+      <c r="A16" s="17">
         <v>3</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B16" s="11" t="str">
         <f t="shared" si="4"/>
         <v>(3,0)</v>
       </c>
-      <c r="C16" s="9" t="str">
+      <c r="C16" s="11" t="str">
         <f t="shared" si="8"/>
         <v>(3,1)</v>
       </c>
-      <c r="D16" s="9" t="str">
+      <c r="D16" s="11" t="str">
         <f t="shared" si="5"/>
         <v>(3,2)</v>
       </c>
-      <c r="E16" s="9" t="str">
+      <c r="E16" s="11" t="str">
         <f t="shared" si="6"/>
         <v>(3,3)</v>
       </c>
-      <c r="F16" s="9" t="str">
+      <c r="F16" s="11" t="str">
         <f t="shared" si="7"/>
         <v>(3,4)</v>
       </c>
-      <c r="G16" s="6" t="str">
+      <c r="G16" s="14" t="str">
         <f t="shared" si="4"/>
         <v>(3,5)</v>
       </c>
       <c r="I16">
         <v>3</v>
       </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9">
-        <v>1</v>
-      </c>
-      <c r="M16" s="9">
+      <c r="J16" s="15">
+        <v>1</v>
+      </c>
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11">
+        <v>1</v>
+      </c>
+      <c r="M16" s="11">
         <v>0</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="11">
         <v>0</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="15">
         <v>1</v>
       </c>
       <c r="Q16" t="str">
@@ -1294,40 +1355,276 @@
         <v>{1,1,1,0,0,1}</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:16">
+      <c r="B18" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
+    <row r="28" spans="1:16">
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="B29" s="10"/>
+      <c r="C29" s="11">
+        <v>150</v>
+      </c>
+      <c r="D29" s="11">
+        <v>180</v>
+      </c>
+      <c r="E29" s="11">
+        <v>210</v>
+      </c>
+      <c r="F29" s="11">
+        <v>240</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="11">
+        <f>C29+20</f>
+        <v>170</v>
+      </c>
+      <c r="M29" s="11">
+        <f t="shared" ref="M29:O32" si="10">D29+20</f>
+        <v>200</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="10"/>
+        <v>230</v>
+      </c>
+      <c r="O29" s="11">
+        <f t="shared" si="10"/>
+        <v>260</v>
+      </c>
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="B30" s="13"/>
+      <c r="C30" s="11">
+        <v>120</v>
+      </c>
+      <c r="D30" s="11">
+        <v>150</v>
+      </c>
+      <c r="E30" s="11">
+        <v>180</v>
+      </c>
+      <c r="F30" s="11">
+        <v>210</v>
+      </c>
+      <c r="G30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="11">
+        <f t="shared" ref="L30:L32" si="11">C30+20</f>
+        <v>140</v>
+      </c>
+      <c r="M30" s="11">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+      <c r="O30" s="11">
+        <f t="shared" si="10"/>
+        <v>230</v>
+      </c>
+      <c r="P30" s="13"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11">
+        <v>90</v>
+      </c>
+      <c r="D31" s="11">
+        <v>120</v>
+      </c>
+      <c r="E31" s="11">
+        <v>150</v>
+      </c>
+      <c r="F31" s="11">
+        <v>180</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11">
+        <f t="shared" si="11"/>
+        <v>110</v>
+      </c>
+      <c r="M31" s="11">
+        <f t="shared" si="10"/>
+        <v>140</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="O31" s="11">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+      <c r="P31" s="13"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11">
+        <v>60</v>
+      </c>
+      <c r="D32" s="11">
+        <v>90</v>
+      </c>
+      <c r="E32" s="11">
+        <v>120</v>
+      </c>
+      <c r="F32" s="11">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="J32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11">
+        <f t="shared" si="11"/>
+        <v>80</v>
+      </c>
+      <c r="M32" s="11">
+        <f t="shared" si="10"/>
+        <v>110</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" si="10"/>
+        <v>140</v>
+      </c>
+      <c r="O32" s="11">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="P32" s="14"/>
+    </row>
+    <row r="33" spans="3:17">
+      <c r="C33">
+        <f>SUM(C29:C32)</f>
+        <v>420</v>
+      </c>
+      <c r="D33">
+        <f t="shared" ref="D33:F33" si="12">SUM(D29:D32)</f>
+        <v>540</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="12"/>
+        <v>660</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="12"/>
+        <v>780</v>
+      </c>
+      <c r="G33">
+        <f>SUM(C33:F33)</f>
+        <v>2400</v>
+      </c>
+      <c r="L33">
+        <f>SUM(L29:L32)</f>
+        <v>500</v>
+      </c>
+      <c r="M33">
+        <f t="shared" ref="M33" si="13">SUM(M29:M32)</f>
+        <v>620</v>
+      </c>
+      <c r="N33">
+        <f t="shared" ref="N33" si="14">SUM(N29:N32)</f>
+        <v>740</v>
+      </c>
+      <c r="O33">
+        <f t="shared" ref="O33" si="15">SUM(O29:O32)</f>
+        <v>860</v>
+      </c>
+      <c r="P33">
+        <f>SUM(L33:O33)</f>
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17">
+      <c r="G34" s="18">
+        <f>G33/100</f>
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="18">
+        <f>P33/100</f>
+        <v>27.2</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17">
+      <c r="G35" s="18">
+        <f>G34*3</f>
+        <v>72</v>
+      </c>
+      <c r="P35" s="18">
+        <f>P34*3</f>
+        <v>81.599999999999994</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J13:O16">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:F16">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>K13=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F32">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>K29=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L29:O32">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>K13=0</formula>
+      <formula>T29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
